--- a/parte 2/dataset_card.xlsx
+++ b/parte 2/dataset_card.xlsx
@@ -93,7 +93,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -106,6 +106,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -515,11 +518,12 @@
     <row r="1" ht="21" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Dataset Card - SimilaridadeTI-FGV</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
+          <t>Similaridade de Palavras de TI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1"/>
+    <row r="3" ht="16" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>Atributo</t>
@@ -530,13 +534,9 @@
           <t>Descrição</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="15" customHeight="1">
+      <c r="C3" s="2" t="n"/>
+    </row>
+    <row r="4" ht="16" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">   Nome do Dataset:</t>
@@ -549,7 +549,7 @@
       </c>
       <c r="C4" s="1" t="inlineStr">
         <is>
-          <t>SimilaridadeTI-FGV</t>
+          <t>Corpus de Similaridade de Palavras de TI</t>
         </is>
       </c>
     </row>
@@ -581,13 +581,13 @@
           <t>Atributo contendo informações sobre onde pode ser obtido e como. Pode ser simplesmente a URL de onde está hospedado: git, hugging face, ...</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">https://github.com/barbaradasilvadapper/T1-PLN </t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>https://github.com/barbaradasilvadapper/T1-PLN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="16" customHeight="1">
       <c r="A7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">   Versão e Data de criação</t>
@@ -604,7 +604,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="16" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">   Versão e Data de atualização</t>
@@ -617,11 +617,11 @@
       </c>
       <c r="C8" s="1" t="inlineStr">
         <is>
-          <t>Versão 1.0 - sem atualizações desde a criação (01/10/2026)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="135" customHeight="1">
+          <t>Versão 1.0 - sem atualizações posteriores</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1">
       <c r="A9" s="1" t="inlineStr">
         <is>
           <t>Natureza dos documentos:</t>
@@ -634,11 +634,11 @@
       </c>
       <c r="C9" s="1" t="inlineStr">
         <is>
-          <t>Pares de palavras tirados do corpus de questões da parte 1 (QuestõesTI-FGV, 2.506 questões da FGV de 2021 a 2026). Os textos foram tokenizados, lematizados e sem stopwords (spaCy pt_core_news_sm); os 200 lemas de maior TF-IDF médio foram embaralhados (semente 42) e combinados em 100 pares sem repetição. Os pares foram anotados manualmente e separadamente por duas integrantes do grupo (Luiza e Rafaela).</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
+          <t>100 pares de palavras formados com os 200 lemas de maior TF-IDF médio do corpus de questões, sorteados dois a dois. Cada par foi anotado à mão, de forma independente, por duas integrantes do grupo (Luiza e Rafaela), numa escala de 1 a 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
       <c r="A10" s="1" t="inlineStr">
         <is>
           <t>Domínio:</t>
@@ -651,11 +651,11 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>Computação / Tecnologia da Informação (vocabulário de questões de concursos públicos)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="45" customHeight="1">
+          <t>Computação / Tecnologia da Informação</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="1" t="inlineStr">
         <is>
           <t>Tarefa:</t>
@@ -672,7 +672,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="16" customHeight="1">
       <c r="A12" s="1" t="inlineStr">
         <is>
           <t>Idioma:</t>
@@ -685,11 +685,11 @@
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>Português (Brasil), com termos técnicos em inglês</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="75" customHeight="1">
+          <t>Português (Brasil)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
       <c r="A13" s="1" t="inlineStr">
         <is>
           <t>Formato:</t>
@@ -702,7 +702,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>CSV UTF-8 (corpus/corpus_similaridade.csv): id do par, palavra 1, palavra 2, tipo de anotação, nome e nota de cada anotadora, média, mediana, amplitude e indicação de revisão. Também: corpus/palavras.csv (as 200 palavras e seu TF-IDF), corpus/pares.csv e corpus/concordancia.json.</t>
+          <t>CSV</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" ht="105" customHeight="1">
+    <row r="18" ht="90" customHeight="1">
       <c r="A18" s="1" t="inlineStr">
         <is>
           <t>Distribuição em classes:</t>
@@ -779,7 +779,7 @@
       </c>
       <c r="C18" s="1" t="inlineStr">
         <is>
-          <t>Escala Likert de 1 a 5: 1 nenhuma semelhança, 2 baixa, 3 moderada, 4 alta, 5 muito alta (sinônimos). Distribuição das notas: Luiza 75 notas 1, 20 notas 2, 5 notas 3; Rafaela 66 notas 1, 28 notas 2, 5 notas 3, 1 nota 4. Média das duas por par: 66 pares com 1, 9 com 1,5, 19 com 2, 1 com 2,5, 4 com 3 e 1 com 3,5.</t>
+          <t>Escala de 1 a 5 (1 nenhuma semelhança, 2 baixa, 3 moderada, 4 alta, 5 sinônimos). Média das duas notas: 66 pares com 1, 9 com 1,5, 19 com 2, 1 com 2,5, 4 com 3 e 1 com 3,5.</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="C19" s="1" t="inlineStr">
         <is>
-          <t>Cada par tem 2 tokens (duas palavras)</t>
+          <t>Cada par tem 2 palavras</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Concordância entre as anotadoras: kappa de Cohen linear 0,79 (quadrático 0,85), concordância exata 89%, Spearman 0,83</t>
+          <t>Concordância entre as anotadoras: kappa linear de 0,79 e Spearman de 0,83</t>
         </is>
       </c>
     </row>
@@ -860,11 +860,11 @@
       </c>
       <c r="C23" s="1" t="inlineStr">
         <is>
-          <t>6 KB (corpus_similaridade.csv)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="409.5" customHeight="1">
+          <t>6 KB</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" s="1" t="inlineStr">
         <is>
           <t>Outras informações:</t>
@@ -877,14 +877,11 @@
       </c>
       <c r="C24" s="1" t="inlineStr">
         <is>
-          <t>A escala tem os mesmos graus da anotação feita em aula: 1 = 0, 2 = 0,25, 3 = 0,5, 4 = 0,75 e 5 = 1. Como os pares foram sorteados, a maioria tem similaridade baixa (95% das notas da Luiza e 94% das da Rafaela são 1 ou 2), o que deixa poucos exemplos de similaridade alta. Palavras sem contexto podem ser ambíguas, e o filtro alfabético exclui termos como C++ e IPv6.</t>
+          <t>A escala equivale à usada em aula (1 = 0, 2 = 0,25, 3 = 0,5, 4 = 0,75, 5 = 1). Como os pares foram sorteados, a maioria tem similaridade baixa.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
 </worksheet>
 </file>